--- a/PaintShop Beste Schema 3M.xlsx
+++ b/PaintShop Beste Schema 3M.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ORD13</t>
+          <t>ORD03</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -506,19 +506,19 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="G2" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="H2" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -527,7 +527,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ORD01</t>
+          <t>ORD06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -542,22 +542,22 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="F3" t="n">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="G3" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H3" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -566,7 +566,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ORD05</t>
+          <t>ORD09</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -578,25 +578,25 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" t="n">
-        <v>6.5</v>
+        <v>9.5</v>
       </c>
       <c r="G4" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="H4" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -605,7 +605,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ORD08</t>
+          <t>ORD28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -617,25 +617,25 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>24.5</v>
+        <v>30.5</v>
       </c>
       <c r="F5" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="G5" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H5" t="n">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -644,7 +644,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ORD14</t>
+          <t>ORD25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -659,16 +659,16 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F6" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="G6" t="n">
-        <v>47.5</v>
+        <v>52.5</v>
       </c>
       <c r="H6" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -683,7 +683,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ORD12</t>
+          <t>ORD20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -695,34 +695,34 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E7" t="n">
-        <v>48.5</v>
+        <v>57.5</v>
       </c>
       <c r="F7" t="n">
-        <v>11</v>
+        <v>7.5</v>
       </c>
       <c r="G7" t="n">
-        <v>59.5</v>
+        <v>65</v>
       </c>
       <c r="H7" t="n">
-        <v>18</v>
+        <v>70</v>
       </c>
       <c r="I7" t="n">
-        <v>41.5</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K7" t="n">
-        <v>249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ORD15</t>
+          <t>ORD26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -737,31 +737,31 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>59.5</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>71.5</v>
+        <v>76</v>
       </c>
       <c r="H8" t="n">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>49.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ORD28</t>
+          <t>ORD17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -773,58 +773,58 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>76.5</v>
+        <v>76</v>
       </c>
       <c r="F9" t="n">
-        <v>11.5</v>
+        <v>7</v>
       </c>
       <c r="G9" t="n">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="H9" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="I9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="K9" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ORD24</t>
+          <t>ORD02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>9.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G10" t="n">
-        <v>103.5</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H10" t="n">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ORD03</t>
+          <t>ORD11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -848,28 +848,28 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="F11" t="n">
-        <v>7.5</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="G11" t="n">
-        <v>7.5</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="H11" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -878,7 +878,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ORD04</t>
+          <t>ORD08</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -887,28 +887,28 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>7.5</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="F12" t="n">
-        <v>7.083333333333333</v>
+        <v>8.75</v>
       </c>
       <c r="G12" t="n">
-        <v>14.58333333333333</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="H12" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -917,7 +917,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ORD06</t>
+          <t>ORD05</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -926,28 +926,28 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>14.58333333333333</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="F13" t="n">
-        <v>6.666666666666667</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>21.25</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="H13" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -956,7 +956,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ORD09</t>
+          <t>ORD14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -965,28 +965,28 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>21.25</v>
+        <v>32.08333333333334</v>
       </c>
       <c r="F14" t="n">
-        <v>7.916666666666667</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="G14" t="n">
-        <v>29.16666666666667</v>
+        <v>42.5</v>
       </c>
       <c r="H14" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
@@ -995,7 +995,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ORD19</t>
+          <t>ORD12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1004,37 +1004,37 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>29.16666666666667</v>
+        <v>43.5</v>
       </c>
       <c r="F15" t="n">
-        <v>8.333333333333334</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="G15" t="n">
-        <v>37.5</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="H15" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>34.66666666666666</v>
       </c>
       <c r="J15" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ORD25</t>
+          <t>ORD15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1043,28 +1043,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>41.5</v>
+        <v>52.66666666666666</v>
       </c>
       <c r="F16" t="n">
-        <v>8.75</v>
+        <v>10</v>
       </c>
       <c r="G16" t="n">
-        <v>50.25</v>
+        <v>62.66666666666666</v>
       </c>
       <c r="H16" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -1073,7 +1073,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ORD16</t>
+          <t>ORD21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1082,37 +1082,37 @@
         </is>
       </c>
       <c r="C17" t="n">
+        <v>8</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="n">
+        <v>62.66666666666666</v>
+      </c>
+      <c r="F17" t="n">
+        <v>7.083333333333333</v>
+      </c>
+      <c r="G17" t="n">
+        <v>69.75</v>
+      </c>
+      <c r="H17" t="n">
+        <v>69</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J17" t="n">
         <v>7</v>
       </c>
-      <c r="D17" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" t="n">
-        <v>53.25</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="G17" t="n">
-        <v>59.91666666666666</v>
-      </c>
-      <c r="H17" t="n">
-        <v>63</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>8</v>
-      </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ORD27</t>
+          <t>ORD18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1121,37 +1121,37 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>59.91666666666666</v>
+        <v>69.75</v>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>8.75</v>
       </c>
       <c r="G18" t="n">
-        <v>64.91666666666666</v>
+        <v>78.5</v>
       </c>
       <c r="H18" t="n">
         <v>78</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ORD22</t>
+          <t>ORD23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1160,28 +1160,28 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>68.91666666666666</v>
+        <v>82.5</v>
       </c>
       <c r="F19" t="n">
-        <v>5.416666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="G19" t="n">
-        <v>74.33333333333333</v>
+        <v>90</v>
       </c>
       <c r="H19" t="n">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -1190,46 +1190,46 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ORD17</t>
+          <t>ORD04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>79.33333333333333</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5.833333333333333</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="G20" t="n">
-        <v>85.16666666666666</v>
+        <v>9.444444444444445</v>
       </c>
       <c r="H20" t="n">
-        <v>85</v>
+        <v>15</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1666666666666572</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="K20" t="n">
-        <v>1.999999999999886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ORD11</t>
+          <t>ORD01</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1238,37 +1238,37 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>13.44444444444444</v>
       </c>
       <c r="F21" t="n">
-        <v>12.77777777777778</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>12.77777777777778</v>
+        <v>21.77777777777778</v>
       </c>
       <c r="H21" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>4.777777777777779</v>
       </c>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>47.77777777777779</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ORD02</t>
+          <t>ORD07</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1277,28 +1277,28 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>12.77777777777778</v>
+        <v>21.77777777777778</v>
       </c>
       <c r="F22" t="n">
-        <v>11.11111111111111</v>
+        <v>7.777777777777778</v>
       </c>
       <c r="G22" t="n">
-        <v>23.88888888888889</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="H22" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -1307,7 +1307,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ORD07</t>
+          <t>ORD10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1316,28 +1316,28 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>25.88888888888889</v>
+        <v>29.55555555555556</v>
       </c>
       <c r="F23" t="n">
-        <v>7.777777777777778</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G23" t="n">
-        <v>33.66666666666666</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="H23" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K23" t="n">
         <v>0</v>
@@ -1346,7 +1346,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ORD10</t>
+          <t>ORD13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1355,28 +1355,28 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" t="n">
         <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>33.66666666666666</v>
+        <v>36.22222222222222</v>
       </c>
       <c r="F24" t="n">
-        <v>6.666666666666667</v>
+        <v>6.111111111111111</v>
       </c>
       <c r="G24" t="n">
-        <v>40.33333333333333</v>
+        <v>42.33333333333333</v>
       </c>
       <c r="H24" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K24" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ORD26</t>
+          <t>ORD16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1394,28 +1394,28 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D25" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E25" t="n">
         <v>45.33333333333333</v>
       </c>
       <c r="F25" t="n">
-        <v>12.22222222222222</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="G25" t="n">
-        <v>57.55555555555555</v>
+        <v>54.22222222222221</v>
       </c>
       <c r="H25" t="n">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -1424,7 +1424,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ORD20</t>
+          <t>ORD19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1433,28 +1433,28 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>57.55555555555555</v>
+        <v>54.22222222222221</v>
       </c>
       <c r="F26" t="n">
-        <v>8.333333333333334</v>
+        <v>11.11111111111111</v>
       </c>
       <c r="G26" t="n">
-        <v>65.88888888888889</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="H26" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K26" t="n">
         <v>0</v>
@@ -1463,7 +1463,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ORD21</t>
+          <t>ORD27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1472,37 +1472,37 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>66.88888888888889</v>
+        <v>65.33333333333333</v>
       </c>
       <c r="F27" t="n">
-        <v>9.444444444444445</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="G27" t="n">
-        <v>76.33333333333333</v>
+        <v>72</v>
       </c>
       <c r="H27" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="I27" t="n">
-        <v>7.333333333333329</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" t="n">
-        <v>51.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ORD18</t>
+          <t>ORD22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1511,37 +1511,37 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E28" t="n">
-        <v>76.33333333333333</v>
+        <v>76</v>
       </c>
       <c r="F28" t="n">
-        <v>11.66666666666667</v>
+        <v>7.222222222222222</v>
       </c>
       <c r="G28" t="n">
-        <v>88</v>
+        <v>83.22222222222223</v>
       </c>
       <c r="H28" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="I28" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>10</v>
       </c>
       <c r="K28" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ORD23</t>
+          <t>ORD24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>92</v>
+        <v>89.22222222222223</v>
       </c>
       <c r="F29" t="n">
-        <v>10</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="G29" t="n">
-        <v>102</v>
+        <v>99.77777777777779</v>
       </c>
       <c r="H29" t="n">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K29" t="n">
         <v>0</v>
